--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0031.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0031.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Concerto Energy của Resonator này chưa đầy</t>
+          <t>Năng lượng Concerto của Resonator này chưa đầy</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Increase Cấp Độ Thăng Hoa Resonator trong trang &lt;color=HighlightB&gt;Resonator - Overview&lt;/color&gt;.</t>
+          <t>Tăng Cấp Độ Thăng Hoa Resonator trong trang &lt;color=HighlightB&gt;Resonator - Tổng Quan&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -707,10 +707,10 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Pha SOL3 được nâng lên thông qua Cấp Liên Minh. &lt;color=HighlightB&gt;Mỗi 10 Cấp Liên Minh tăng Pha SOL3 lên 1.&lt;/color&gt;
-Khi đạt đến Cấp Liên Minh &lt;color=HighlightB&gt;20, 40 và 60&lt;/color&gt;, hãy hoàn thành nhiệm vụ &lt;color=HighlightB&gt;Thăng Tiến Pha&lt;/color&gt; tương ứng để tiếp tục tăng Cấp Liên Minh.
-Nếu chưa hoàn thành nhiệm vụ Thăng Tiến Pha tương ứng, Pha SOL3 sẽ không thể nâng lên khi Cấp Liên Minh đạt đến giới hạn.
-Truy cập mục Nhiệm Vụ để hoàn thành nhiệm vụ Thăng Tiến Pha, từ đó nâng giới hạn Cấp Liên Minh.</t>
+          <t>Pha SOL3 được nâng lên thông qua Cấp Độ Liên Minh. &lt;color=HighlightB&gt;Cứ 10 Cấp Độ Liên Minh sẽ tăng Pha SOL3 lên 1.&lt;/color&gt;
+Khi đạt đến Cấp Độ Liên Minh &lt;color=HighlightB&gt;20, 40 và 60&lt;/color&gt;, hãy hoàn thành nhiệm vụ &lt;color=HighlightB&gt;Thăng Tiến Pha&lt;/color&gt; tương ứng để tiếp tục tăng Cấp Độ Liên Minh.
+Nếu chưa hoàn thành nhiệm vụ Thăng Tiến Pha tương ứng, Pha SOL3 sẽ không thể nâng lên khi Cấp Độ Liên Minh đạt đến giới hạn.
+Truy cập mục Nhiệm Vụ để hoàn thành nhiệm vụ Thăng Tiến Pha, từ đó nâng giới hạn Cấp Độ Liên Minh.</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Cậu muốn Dịch Chuyển Nhanh đến Điểm Phát Tín Resonance gần nhất và theo dõi mục tiêu không?</t>
+          <t>Cậu muốn Dịch Chuyển Nhanh đến Điểm Phát Tín Cộng Hưởng gần nhất và theo dõi mục tiêu không?</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Thả nút Wheel sẽ kích hoạt tính năng mà cần gạt đang chỉ vào.</t>
+          <t>Thả nút Bánh Xe sẽ kích hoạt tính năng mà cần gạt đang chỉ vào.</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Tăng cường Forte</t>
+          <t>Tăng Cường Mạch Năng Lực</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Buff Kỹ thuật</t>
+          <t>Tăng cường Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Sóng Enemies: {0}</t>
+          <t>Sóng Kẻ Thù: {0}</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Chức năng thay đổi ngoại hình của Rover đang trong Cooldown chiêu.</t>
+          <t>Chức năng thay đổi ngoại hình của Vận Mệnh Giả đang trong thời gian hồi chiêu.</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Kích hoạt Mạch Resonance tại Hang Thợ Săn - Sanguis Plateaus</t>
+          <t>Kích hoạt Mạch Cộng Hưởng tại Hang Thợ Săn - Cao Nguyên Sanguis</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Mở Thiết bị đầu cuối Resonance ở Thành phố Ragunna trong Nhiệm vụ Main "Làn Gió Thiêng Thường Xuyên Thổi"</t>
+          <t>Mở Thiết bị đầu cuối Cộng Hưởng ở Thành phố Ragunna trong Nhiệm vụ Chính "Làn Gió Thiêng Thường Xuyên Thổi"</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Mở Thiết bị đầu cuối Resonance ở Thành phố Ragunna trong Nhiệm vụ Main "Làn Gió Thiêng Thường Xuyên Thổi"</t>
+          <t>Mở Thiết bị đầu cuối Cộng Hưởng ở Thành phố Ragunna trong Nhiệm vụ Chính "Làn Gió Thiêng Thường Xuyên Thổi"</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Mục tiêu Yêu Cầu chỉ xuất hiện vào ban đêm. Chuyển sang Fishing Ban Night?</t>
+          <t>Mục tiêu Yêu Cầu chỉ xuất hiện vào ban đêm. Chuyển sang Câu Cá Ban Đêm?</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Lỗi dữ liệu thời gian hỗ trợ</t>
+          <t>Lỗi dữ liệu thời gian ủng hộ</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Lỗi dữ liệu thời gian hỗ trợ</t>
+          <t>Lỗi dữ liệu thời gian ủng hộ</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Kênh Chat Trực Tuyến đang trong Cooldown chiêu</t>
+          <t>Kênh Trò Chuyện Trực Tuyến đang trong thời gian hồi chiêu</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Thao tác đang trong Cooldown chiêu</t>
+          <t>Thao tác đang trong thời gian hồi chiêu</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Thử thách Spectro Frazzle</t>
+          <t>Thử Thách Rối Loạn Spectro</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Thử thách Glacio Chafe</t>
+          <t>Thử Thách Xước Băng Giá</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Challenge Erosion Aero</t>
+          <t>Thử Thách Xói Mòn Aero</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Challenge Bùng Nổ Fusion</t>
+          <t>Thử Thách Bùng Nổ Hợp Nhất</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi đăng nhập vào Terminal tại Điểm Kết Nối Jinzhou trong Nhiệm Vụ Chính "Âm Vang Đầu Tiên."</t>
+          <t>Mở khóa sau khi đăng nhập vào Thiết bị đầu cuối tại Điểm Kết Nối Jinzhou trong Nhiệm Vụ Chính "Âm Vang Đầu Tiên."</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Kỹ năng đã chọn không hợp lệ.</t>
+          <t>Kỹ năng đã chọn không hợp lệ</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Cấu hình Kỹ năng trống.</t>
+          <t>Cấu hình kỹ năng trống.</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Không tìm thấy Trigger.</t>
+          <t>Không tìm thấy kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Không tìm thấy dữ liệu Buff Echo.</t>
+          <t>Không tìm thấy dữ liệu Tăng Cường Echo.</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình buff Echo.</t>
+          <t>Không tìm thấy cấu hình buff Echo</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Đơn vị kẻ địch trống.</t>
+          <t>Đơn vị kẻ địch không tồn tại.</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Cấu hình kẻ địch trống.</t>
+          <t>Cấu hình kẻ địch không tồn tại.</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3637,7 @@
       <c r="M49" t="inlineStr">
         <is>
           <t>Kẻ địch tinh nhuệ trong khu vực này đang ở phía trước. Ngươi có chắc muốn đối đầu với một đối thủ mạnh như vậy vào lúc này không?
-Để tăng cơ hội chiến thắng, hãy thử nâng Cấp Glory bằng cách hoàn thành các thử thách phù hợp ở các Biểu Ngữ khác trước.</t>
+Để tăng cơ hội chiến thắng, hãy thử nâng Cấp Vinh Quang bằng cách hoàn thành các thử thách phù hợp ở các Biểu Ngữ khác trước.</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Mục tiêu gỡ bỏ không tồn tại</t>
+          <t>Mục tiêu gỡ bỏ không tồn tại.</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Lỗi mục tiêu</t>
+          <t>Lỗi mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -3834,9 +3834,9 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>1. Exchange Waveplate tại Tinh Thể Tàn Dư để nhận phần thưởng Tacet Field tương ứng, bao gồm Dội Âm và vật liệu nâng cấp.
-2. Bạn phải hoàn thành thử thách Tacet Field mục tiêu và nhận phần thưởng gốc trước khi có thể nhận lại bộ phần thưởng tương tự từ giao diện này.
-3. Mỗi tuần, Fantasies of the Thousand Gateways cung cấp 2 lượt nhận miễn phí hai phần thưởng đầu tiên từ Tinh Thể Tàn Dư mà không cần Waveplate. Lượt nhận phần thưởng miễn phí không được chuyển sang tuần tiếp theo.</t>
+          <t>1. Đổi Waveplate tại Tinh Thể Tàn Dư để nhận phần thưởng Tổ Tacet tương ứng, bao gồm Dội Âm và vật liệu nâng cấp.
+2. Bạn phải hoàn thành thử thách Tổ Tacet mục tiêu và nhận phần thưởng gốc trước khi có thể nhận lại bộ phần thưởng tương tự từ giao diện này.
+3. Mỗi tuần, Ảo Ảnh Ngàn Cánh Cổng cung cấp 2 lượt nhận miễn phí hai phần thưởng đầu tiên từ Tinh Thể Tàn Dư mà không cần Waveplate. Lượt nhận phần thưởng miễn phí không được chuyển sang tuần tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands"</t>
+          <t>Kích hoạt Mạch Cộng hưởng tại Học viện Startorch trong Nhiệm vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên"</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands" để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và kích hoạt Mạng Lưới Cộng Hưởng tại Học viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Băng Giá" để mở khóa</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands"</t>
+          <t>Kích hoạt Mạch Cộng hưởng tại Học viện Startorch trong Nhiệm vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên"</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 27 và kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands" để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 27 và kích hoạt Resonance Nexus tại Học viện Startorch trong Nhiệm vụ Chính "What Burns Beneath Frostlands" để mở khóa</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands" để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và kích hoạt Mạng Lưới Cộng Hưởng tại Học viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Băng Giá" để mở khóa</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands"</t>
+          <t>Kích hoạt Mạch Cộng hưởng tại Học viện Startorch trong Nhiệm vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên"</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands"</t>
+          <t>Kích hoạt Mạch Cộng hưởng tại Học viện Startorch trong Nhiệm vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên"</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Không có Echoes nào có thể điều chỉnh theo chỉ số mục tiêu.</t>
+          <t>Không có Echo nào có thể điều chỉnh theo chỉ số mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Resonator đã chọn đã đạt đến giới hạn Chuỗi Resonance.</t>
+          <t>Resonator đã chọn đã đạt đến giới hạn Resonance Chain.</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands" để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và kích hoạt Mạng Lưới Cộng Hưởng tại Học viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Băng Giá" để mở khóa</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands"</t>
+          <t>Kích hoạt Mạch Cộng hưởng tại Học viện Startorch trong Nhiệm vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên"</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands"</t>
+          <t>Kích hoạt Mạch Cộng hưởng tại Học viện Startorch trong Nhiệm vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên"</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Không thể sử dụng kỹ năng</t>
+          <t>Kỹ năng sử dụng thất bại</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình Kỹ năng</t>
+          <t>Không tìm thấy cấu hình kỹ năng</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands" để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và kích hoạt Mạng Lưới Cộng Hưởng tại Học viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Băng Giá" để mở khóa</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands"</t>
+          <t>Kích hoạt Mạch Cộng hưởng tại Học viện Startorch trong Nhiệm vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên"</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm Vụ Chính "What Burns Beneath Frostlands" để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và kích hoạt Nexus Cộng Hưởng tại Học viện Startorch trong Nhiệm Vụ Chính "Lửa Cháy Dưới Băng Giá" để mở khóa</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands" để mở khóa</t>
+          <t>Kích hoạt Mạch Cộng hưởng tại Học viện Startorch trong Nhiệm vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên" để mở khóa</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm Vụ Chính "What Burns Beneath Frostlands" để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và kích hoạt Nexus Cộng Hưởng tại Học viện Startorch trong Nhiệm Vụ Chính "Lửa Cháy Dưới Băng Giá" để mở khóa</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands"</t>
+          <t>Kích hoạt Mạch Cộng hưởng tại Học viện Startorch trong Nhiệm vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên"</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands" để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và kích hoạt Mạng Lưới Cộng Hưởng tại Học viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Băng Giá" để mở khóa</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus Học Viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên."</t>
+          <t>Kích hoạt Mạng Lưới Cộng Hưởng Học Viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên."</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands" để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và kích hoạt Mạng Lưới Cộng Hưởng tại Học viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Băng Giá" để mở khóa</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands" để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và kích hoạt Mạng Lưới Cộng Hưởng tại Học viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Băng Giá" để mở khóa</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Đạt Cấp Liên Minh 14 và kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands" để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và kích hoạt Mạng Lưới Cộng Hưởng tại Học viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Băng Giá" để mở khóa</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands"</t>
+          <t>Kích hoạt Mạch Cộng hưởng tại Học viện Startorch trong Nhiệm vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên"</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Chính "What Burns Beneath Frostlands"</t>
+          <t>Kích hoạt Mạch Cộng hưởng tại Học viện Startorch trong Nhiệm vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên"</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus Học Viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên."</t>
+          <t>Kích hoạt Mạng Lưới Cộng Hưởng Học Viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên."</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Nexus Học Viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên."</t>
+          <t>Kích hoạt Mạng Lưới Cộng Hưởng Học Viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên."</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Vũ khí mục tiêu bị khóa</t>
+          <t>Mục tiêu vũ khí đã bị khóa</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Vũ khí mục tiêu đã liên kết</t>
+          <t>Vũ khí mục tiêu đã được liên kết</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Bảng xếp hạng Persona Pinball đang trong Cooldown</t>
+          <t>Bảng Xếp Hạng Persona Pinball Đang Trong Thời Gian Chờ</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Lỗi số lượng Resonance Mode</t>
+          <t>Lỗi số lượng Chế Độ Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -29520,7 +29520,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Viên bổ sung chứa một lượng nhỏ Năng Lượng Tacetite. Có thể sử dụng trong mô-đun lõi của Vũ Khí Tacetite để tăng công suất đầu ra. Weapons là đồng minh của Resonators, còn Tacetite chính là thức ăn của chúng. Chỉ khi nuôi dưỡng vũ khí tốt, chúng mới trở nên tiện dụng và mạnh mẽ hơn trong trận chiến.</t>
+          <t>Viên bổ sung chứa một lượng nhỏ Năng Lượng Tacetite. Có thể sử dụng trong mô-đun lõi của Vũ Khí Tacetite để tăng công suất đầu ra. Vũ khí là đồng minh của Resonators, còn Tacetite chính là thức ăn của chúng. Chỉ khi nuôi dưỡng vũ khí tốt, chúng mới trở nên tiện dụng và mạnh mẽ hơn trong trận chiến.</t>
         </is>
       </c>
     </row>
@@ -29910,7 +29910,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Vật liệu trung cấp dùng để Tiến Hóa Vũ Khí và Skill Nâng cấp cho Resonators sử dụng Pistols.</t>
+          <t>Vật liệu trung cấp dùng để Tiến Hóa Vũ Khí và Skill Nâng cấp cho Resonators sử dụng Súng.</t>
         </is>
       </c>
     </row>
@@ -29975,7 +29975,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Vật liệu cao cấp dùng để Tiến Hóa Vũ Khí và Skill Nâng cấp cho Resonators Pistols.</t>
+          <t>Vật liệu cao cấp dùng để Tiến Hóa Vũ Khí và Skill Nâng cấp cho Resonators Súng.</t>
         </is>
       </c>
     </row>
@@ -30170,7 +30170,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Vật liệu trung cấp dùng để Tiến Hóa Vũ Khí và Skill Nâng cấp cho Resonators sử dụng Rectifier.</t>
+          <t>Vật liệu trung cấp dùng để Tiến Hóa Vũ Khí và Skill Nâng cấp cho Resonators sử dụng Pháp khí.</t>
         </is>
       </c>
     </row>
@@ -30235,7 +30235,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Vật liệu cao cấp dùng để Tiến Hóa Vũ Khí và Skill Nâng cấp cho Resonators Rectifier.</t>
+          <t>Vật liệu cao cấp dùng để Tiến Hóa Vũ Khí và Skill Nâng cấp cho Resonators Pháp khí.</t>
         </is>
       </c>
     </row>
@@ -30365,7 +30365,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Vật liệu cơ bản dùng để Tiến Hóa Vũ Khí và Skill Nâng cấp cho Resonators dùng Broadblade.</t>
+          <t>Vật liệu cơ bản dùng để Tiến Hóa Vũ Khí và Skill Nâng cấp cho Resonators dùng Đại kiếm.</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Vật liệu trung cấp dùng để Tiến Hóa Vũ Khí và Skill Nâng cấp cho Resonators sử dụng Broadblade.</t>
+          <t>Vật liệu trung cấp dùng để Tiến Hóa Vũ Khí và Skill Nâng cấp cho Resonators sử dụng Đại kiếm.</t>
         </is>
       </c>
     </row>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Vật liệu cao cấp dùng để Tiến Hóa Vũ Khí và Skill Nâng cấp cho Resonators Broadblade.</t>
+          <t>Vật liệu cao cấp dùng để Tiến Hóa Vũ Khí và Skill Nâng cấp cho Resonators Đại kiếm.</t>
         </is>
       </c>
     </row>
@@ -30755,7 +30755,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Vật liệu trung cấp dùng để Tiến Hóa Vũ Khí và Skill Nâng cấp cho Resonators sử dụng Gauntlets.</t>
+          <t>Vật liệu trung cấp dùng để Tiến Hóa Vũ Khí và Skill Nâng cấp cho Resonators sử dụng Găng tay.</t>
         </is>
       </c>
     </row>
@@ -30820,7 +30820,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Vật liệu cao cấp dùng để Tiến Hóa Vũ Khí và Skill Nâng cấp cho Resonators Gauntlets.</t>
+          <t>Vật liệu cao cấp dùng để Tiến Hóa Vũ Khí và Skill Nâng cấp cho Resonators Găng tay.</t>
         </is>
       </c>
     </row>
